--- a/_pythonscripts/all-members.xlsx
+++ b/_pythonscripts/all-members.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a37f0bd66b0f646b/Documents/Website/sajidbuet/sajidbuet.github.io/_pythonscripts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a37f0bd66b0f646b/Documents/Website/sajidbuet/hugo-research-group/_pythonscripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="151" documentId="11_3D01AA1F5550F20E62355476585DCE3A8747F3F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BD6E8A0-D564-4C9B-A6D7-DC388906CE66}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2006" yWindow="3274" windowWidth="14400" windowHeight="7217" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -825,22 +825,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.21875" customWidth="1"/>
-    <col min="11" max="11" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.4609375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.23046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.23046875" customWidth="1"/>
+    <col min="11" max="11" width="28.69140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -913,7 +913,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -951,7 +951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -989,7 +989,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>73</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>136</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>90</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>92</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>96</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>107</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>134</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>112</v>
       </c>

--- a/_pythonscripts/all-members.xlsx
+++ b/_pythonscripts/all-members.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a37f0bd66b0f646b/Documents/Website/sajidbuet/hugo-research-group/_pythonscripts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sajid\OneDrive\Documents\Website\sajidbuet\sajidbuet.github.io\_pythonscripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="11_3D01AA1F5550F20E62355476585DCE3A8747F3F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BD6E8A0-D564-4C9B-A6D7-DC388906CE66}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE077B6-79A8-457C-B6F6-F3E2D20F4216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2006" yWindow="3274" windowWidth="14400" windowHeight="7217" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
   <si>
     <t>foldername</t>
   </si>
@@ -100,15 +100,6 @@
     <t>Hybrid Metal-Dielectric Nanostructures Integrated Heterojunction Thin Film Solar Cell for Efficiency</t>
   </si>
   <si>
-    <t>0423062319-mesbah</t>
-  </si>
-  <si>
-    <t>0423062319</t>
-  </si>
-  <si>
-    <t>Md. Mesbah Uddin</t>
-  </si>
-  <si>
     <t>0423062522-Abu-Md-Raihan</t>
   </si>
   <si>
@@ -157,30 +148,9 @@
     <t>Jayed Hasan Rakib</t>
   </si>
   <si>
-    <t>0424062385-Md-Shahinul-Islam</t>
-  </si>
-  <si>
-    <t>0424062385</t>
-  </si>
-  <si>
-    <t>Md. Shahinul Islam</t>
-  </si>
-  <si>
-    <t>1024062129-Md-Tasrif-Prodhan</t>
-  </si>
-  <si>
-    <t>1024062129</t>
-  </si>
-  <si>
-    <t>Md. Tasrif Prodhan</t>
-  </si>
-  <si>
     <t>EEPS</t>
   </si>
   <si>
-    <t>DU</t>
-  </si>
-  <si>
     <t>1024062144-Tanvir-Ahmed</t>
   </si>
   <si>
@@ -190,82 +160,10 @@
     <t>Tanvir Ahmed</t>
   </si>
   <si>
-    <t>1024062303-Md-Emad-Hossain-Likhon</t>
-  </si>
-  <si>
-    <t>1024062303</t>
-  </si>
-  <si>
-    <t>Md. Emad Hossain Likhon</t>
-  </si>
-  <si>
     <t>EP</t>
   </si>
   <si>
-    <t>1024062333-Dipika-Rani-Nath</t>
-  </si>
-  <si>
-    <t>1024062333</t>
-  </si>
-  <si>
-    <t>Dipika Rani Nath</t>
-  </si>
-  <si>
     <t>BUET</t>
-  </si>
-  <si>
-    <t>1024062339-Subhan-Zawad-Bihan</t>
-  </si>
-  <si>
-    <t>1024062339</t>
-  </si>
-  <si>
-    <t>Subhan Zawad Bihan</t>
-  </si>
-  <si>
-    <t>1024062371-Farzana-Yesmin</t>
-  </si>
-  <si>
-    <t>1024062371</t>
-  </si>
-  <si>
-    <t>Farzana Yesmin</t>
-  </si>
-  <si>
-    <t>1024062374-Junayet-Hossaain</t>
-  </si>
-  <si>
-    <t>1024062374</t>
-  </si>
-  <si>
-    <t>Junayet Hossaain</t>
-  </si>
-  <si>
-    <t>1024062377-Ramisa-Tahsin-Shreya</t>
-  </si>
-  <si>
-    <t>1024062377</t>
-  </si>
-  <si>
-    <t>Ramisa Tahsin Shreya</t>
-  </si>
-  <si>
-    <t>1024062404-Bokhtiar-Foysol-Himon</t>
-  </si>
-  <si>
-    <t>1024062404</t>
-  </si>
-  <si>
-    <t>Bokhtiar Foysol Himon</t>
-  </si>
-  <si>
-    <t>1024062406-Md-Tarique-Habibullah</t>
-  </si>
-  <si>
-    <t>1024062406</t>
-  </si>
-  <si>
-    <t>Md Tarique Habibullah</t>
   </si>
   <si>
     <t>20-azim-sikder</t>
@@ -824,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
@@ -866,13 +764,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
@@ -892,25 +790,25 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I2" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="J2" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K2" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -921,28 +819,28 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="J3" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="L3">
         <v>2025</v>
@@ -962,36 +860,36 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="L4">
         <v>2025</v>
       </c>
       <c r="M4" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1000,25 +898,25 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="L5">
         <v>2025</v>
@@ -1038,25 +936,25 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I6" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K6" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -1070,57 +968,57 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I7" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K7" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1134,25 +1032,25 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I9" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1166,802 +1064,450 @@
         <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K10" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12">
+        <v>1024064011</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="I12" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="K12" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13">
+        <v>2006022</v>
+      </c>
+      <c r="D13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
         <v>50</v>
       </c>
-      <c r="E13" t="s">
+      <c r="H13" t="s">
         <v>51</v>
       </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" t="s">
-        <v>125</v>
+      <c r="I13">
+        <v>2020</v>
       </c>
       <c r="J13" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14">
+        <v>2006008</v>
+      </c>
+      <c r="D14" t="s">
         <v>53</v>
       </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
       <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" t="s">
-        <v>125</v>
+      <c r="I14">
+        <v>2020</v>
       </c>
       <c r="J14" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="C15">
+        <v>2006175</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>140</v>
-      </c>
-      <c r="I15" t="s">
-        <v>125</v>
+        <v>51</v>
+      </c>
+      <c r="I15">
+        <v>2020</v>
       </c>
       <c r="J15" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K15" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="C16">
+        <v>2006192</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I16" t="s">
-        <v>125</v>
+        <v>51</v>
+      </c>
+      <c r="I16">
+        <v>2020</v>
       </c>
       <c r="J16" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="C17">
+        <v>2006173</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H17" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" t="s">
-        <v>125</v>
+        <v>51</v>
+      </c>
+      <c r="I17">
+        <v>2020</v>
       </c>
       <c r="J17" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>2006095</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
-      </c>
-      <c r="I18" t="s">
-        <v>125</v>
+        <v>51</v>
+      </c>
+      <c r="I18">
+        <v>2020</v>
       </c>
       <c r="J18" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s">
-        <v>131</v>
+        <v>99</v>
+      </c>
+      <c r="L19">
+        <v>2025</v>
+      </c>
+      <c r="M19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s">
-        <v>131</v>
+        <v>99</v>
+      </c>
+      <c r="L20">
+        <v>2023</v>
+      </c>
+      <c r="M20" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
         <v>76</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" t="s">
+        <v>94</v>
+      </c>
+      <c r="K21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L21">
+        <v>2024</v>
+      </c>
+      <c r="M21" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>140</v>
-      </c>
-      <c r="I21" t="s">
-        <v>125</v>
-      </c>
-      <c r="J21" t="s">
-        <v>128</v>
-      </c>
-      <c r="K21" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s">
-        <v>131</v>
+        <v>99</v>
+      </c>
+      <c r="L22">
+        <v>2025</v>
+      </c>
+      <c r="M22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23">
-        <v>1024064011</v>
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
-      </c>
-      <c r="I23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J23" t="s">
-        <v>139</v>
-      </c>
-      <c r="K23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
         <v>82</v>
-      </c>
-      <c r="C24">
-        <v>2006022</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24">
-        <v>2020</v>
-      </c>
-      <c r="J24" t="s">
-        <v>129</v>
-      </c>
-      <c r="K24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25">
-        <v>2006008</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25">
-        <v>2020</v>
-      </c>
-      <c r="J25" t="s">
-        <v>129</v>
-      </c>
-      <c r="K25" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26">
-        <v>2006175</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" t="s">
-        <v>63</v>
-      </c>
-      <c r="G26" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26">
-        <v>2020</v>
-      </c>
-      <c r="J26" t="s">
-        <v>129</v>
-      </c>
-      <c r="K26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27">
-        <v>2006192</v>
-      </c>
-      <c r="D27" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27">
-        <v>2020</v>
-      </c>
-      <c r="J27" t="s">
-        <v>129</v>
-      </c>
-      <c r="K27" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28">
-        <v>2006173</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" t="s">
-        <v>63</v>
-      </c>
-      <c r="G28" t="s">
-        <v>84</v>
-      </c>
-      <c r="H28" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28">
-        <v>2020</v>
-      </c>
-      <c r="J28" t="s">
-        <v>129</v>
-      </c>
-      <c r="K28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29">
-        <v>2006095</v>
-      </c>
-      <c r="D29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29">
-        <v>2020</v>
-      </c>
-      <c r="J29" t="s">
-        <v>129</v>
-      </c>
-      <c r="K29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" t="s">
-        <v>118</v>
-      </c>
-      <c r="G30" t="s">
-        <v>99</v>
-      </c>
-      <c r="H30" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" t="s">
-        <v>121</v>
-      </c>
-      <c r="J30" t="s">
-        <v>128</v>
-      </c>
-      <c r="K30" t="s">
-        <v>133</v>
-      </c>
-      <c r="L30">
-        <v>2025</v>
-      </c>
-      <c r="M30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" t="s">
-        <v>121</v>
-      </c>
-      <c r="J31" t="s">
-        <v>128</v>
-      </c>
-      <c r="K31" t="s">
-        <v>133</v>
-      </c>
-      <c r="L31">
-        <v>2023</v>
-      </c>
-      <c r="M31" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" t="s">
-        <v>122</v>
-      </c>
-      <c r="J32" t="s">
-        <v>128</v>
-      </c>
-      <c r="K32" t="s">
-        <v>133</v>
-      </c>
-      <c r="L32">
-        <v>2024</v>
-      </c>
-      <c r="M32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33" t="s">
-        <v>135</v>
-      </c>
-      <c r="H33" t="s">
-        <v>100</v>
-      </c>
-      <c r="I33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J33" t="s">
-        <v>128</v>
-      </c>
-      <c r="K33" t="s">
-        <v>133</v>
-      </c>
-      <c r="L33">
-        <v>2025</v>
-      </c>
-      <c r="M33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="G34" t="s">
-        <v>115</v>
-      </c>
-      <c r="H34" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/_pythonscripts/all-members.xlsx
+++ b/_pythonscripts/all-members.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sajid\OneDrive\Documents\Website\sajidbuet\sajidbuet.github.io\_pythonscripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a37f0bd66b0f646b/Documents/Website/sajidbuet/sajidbuet.github.io/_pythonscripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE077B6-79A8-457C-B6F6-F3E2D20F4216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{FBE077B6-79A8-457C-B6F6-F3E2D20F4216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24F98B5-4EED-4C92-9304-64D6D4C32A3E}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
   <si>
     <t>foldername</t>
   </si>
@@ -139,15 +139,6 @@
     <t>Naved Sadat Yamin</t>
   </si>
   <si>
-    <t>0424062380-Jayed-Hasan-Rakib</t>
-  </si>
-  <si>
-    <t>0424062380</t>
-  </si>
-  <si>
-    <t>Jayed Hasan Rakib</t>
-  </si>
-  <si>
     <t>EEPS</t>
   </si>
   <si>
@@ -166,48 +157,12 @@
     <t>BUET</t>
   </si>
   <si>
-    <t>20-azim-sikder</t>
-  </si>
-  <si>
-    <t>Md. Azim Sikder</t>
-  </si>
-  <si>
     <t>UG Student</t>
   </si>
   <si>
     <t>Undergrad Students</t>
   </si>
   <si>
-    <t>20-md-solaiman</t>
-  </si>
-  <si>
-    <t>Md. Solaiman</t>
-  </si>
-  <si>
-    <t>20-meherin-tasfia</t>
-  </si>
-  <si>
-    <t>Meherin Tasfia</t>
-  </si>
-  <si>
-    <t>20-nafis-ahmed</t>
-  </si>
-  <si>
-    <t>Nafis Ahmed</t>
-  </si>
-  <si>
-    <t>20-sakif-imam</t>
-  </si>
-  <si>
-    <t>Md. Sakif Imam</t>
-  </si>
-  <si>
-    <t>20-tanvirul-islam</t>
-  </si>
-  <si>
-    <t>Md. Tanvirul Islam</t>
-  </si>
-  <si>
     <t>A-0421062305-Md-Mahfuzul-Haque</t>
   </si>
   <si>
@@ -358,7 +313,25 @@
     <t>Graduated with MSc (July 2025)</t>
   </si>
   <si>
-    <t>Defended MSc (September 2025)</t>
+    <t>Addrita Basak Nodi</t>
+  </si>
+  <si>
+    <t>2106147-addrita-basak-nodi</t>
+  </si>
+  <si>
+    <t>Ramima Mumtarin</t>
+  </si>
+  <si>
+    <t>2106173-ramima-mumtarin</t>
+  </si>
+  <si>
+    <t>2106136-gopal-gosh</t>
+  </si>
+  <si>
+    <t>Gopal Gosh</t>
+  </si>
+  <si>
+    <t>Graduated with MSc (September 2025)</t>
   </si>
 </sst>
 </file>
@@ -722,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
@@ -764,13 +737,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
@@ -790,25 +763,25 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -819,28 +792,28 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="L3">
         <v>2025</v>
@@ -860,36 +833,36 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" t="s">
         <v>94</v>
-      </c>
-      <c r="K4" t="s">
-        <v>109</v>
       </c>
       <c r="L4">
         <v>2025</v>
       </c>
       <c r="M4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -898,25 +871,25 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" t="s">
         <v>84</v>
-      </c>
-      <c r="G5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" t="s">
-        <v>99</v>
       </c>
       <c r="L5">
         <v>2025</v>
@@ -936,25 +909,25 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -968,7 +941,7 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
         <v>32</v>
@@ -977,16 +950,16 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1000,25 +973,25 @@
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1032,39 +1005,39 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J9" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -1073,161 +1046,161 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11">
+        <v>1024064011</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>42</v>
-      </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C12">
-        <v>1024064011</v>
+        <v>2106147</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
         <v>46</v>
       </c>
-      <c r="F12" t="s">
+      <c r="I12">
+        <v>2021</v>
+      </c>
+      <c r="J12" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" t="s">
         <v>83</v>
-      </c>
-      <c r="G12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C13">
-        <v>2006022</v>
+        <v>2106173</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" t="s">
         <v>46</v>
       </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" t="s">
-        <v>51</v>
-      </c>
       <c r="I13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C14">
-        <v>2006008</v>
+        <v>2106136</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s">
         <v>46</v>
       </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" t="s">
-        <v>51</v>
-      </c>
       <c r="I14">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15">
-        <v>2006175</v>
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
         <v>50</v>
@@ -1235,279 +1208,151 @@
       <c r="H15" t="s">
         <v>51</v>
       </c>
-      <c r="I15">
-        <v>2020</v>
+      <c r="I15" t="s">
+        <v>72</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="L15">
+        <v>2025</v>
+      </c>
+      <c r="M15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
         <v>56</v>
-      </c>
-      <c r="C16">
-        <v>2006192</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" t="s">
-        <v>50</v>
       </c>
       <c r="H16" t="s">
         <v>51</v>
       </c>
-      <c r="I16">
-        <v>2020</v>
+      <c r="I16" t="s">
+        <v>72</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="L16">
+        <v>2023</v>
+      </c>
+      <c r="M16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>58</v>
       </c>
-      <c r="C17">
-        <v>2006173</v>
+      <c r="C17" t="s">
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
         <v>51</v>
       </c>
-      <c r="I17">
-        <v>2020</v>
+      <c r="I17" t="s">
+        <v>73</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="L17">
+        <v>2024</v>
+      </c>
+      <c r="M17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18">
-        <v>2006095</v>
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
         <v>51</v>
       </c>
-      <c r="I18">
-        <v>2020</v>
+      <c r="I18" t="s">
+        <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="L18">
+        <v>2025</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" t="s">
-        <v>94</v>
-      </c>
-      <c r="K19" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19">
-        <v>2025</v>
-      </c>
-      <c r="M19" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" t="s">
-        <v>87</v>
-      </c>
-      <c r="J20" t="s">
-        <v>94</v>
-      </c>
-      <c r="K20" t="s">
-        <v>99</v>
-      </c>
-      <c r="L20">
-        <v>2023</v>
-      </c>
-      <c r="M20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" t="s">
-        <v>99</v>
-      </c>
-      <c r="L21">
-        <v>2024</v>
-      </c>
-      <c r="M21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" t="s">
-        <v>94</v>
-      </c>
-      <c r="K22" t="s">
-        <v>99</v>
-      </c>
-      <c r="L22">
-        <v>2025</v>
-      </c>
-      <c r="M22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
